--- a/diseases/d142/2026-2029.xlsx
+++ b/diseases/d142/2026-2029.xlsx
@@ -20801,13 +20801,13 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R121" t="n">
-        <v>0</v>
+        <v>0.01778809170864137</v>
       </c>
       <c r="S121" t="inlineStr">
         <is>
@@ -20960,10 +20960,10 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U122" t="inlineStr">
         <is>
@@ -21305,7 +21305,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>235728</v>
+        <v>235729</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d142/2026-2029.xlsx
+++ b/diseases/d142/2026-2029.xlsx
@@ -18402,13 +18402,13 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>18819</v>
+        <v>18940</v>
       </c>
       <c r="O105" t="n">
-        <v>18819</v>
+        <v>18940</v>
       </c>
       <c r="R105" t="n">
-        <v>69.11864563154293</v>
+        <v>69.56305586170483</v>
       </c>
       <c r="S105" t="inlineStr">
         <is>
@@ -20617,12 +20617,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -20647,22 +20647,22 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N120" t="n">
-        <v>1071</v>
+        <v>1755</v>
       </c>
       <c r="O120" t="n">
-        <v>1071</v>
+        <v>1755</v>
       </c>
       <c r="R120" t="n">
-        <v>3.933581458705695</v>
+        <v>1.43349875527792</v>
       </c>
       <c r="S120" t="inlineStr">
         <is>
@@ -20695,42 +20695,42 @@
       </c>
       <c r="AV120" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB120" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC120" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -20762,12 +20762,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -20801,95 +20801,81 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>1</v>
+        <v>1071</v>
       </c>
       <c r="O121" t="n">
-        <v>1</v>
+        <v>1071</v>
       </c>
       <c r="R121" t="n">
-        <v>0.01778809170864137</v>
+        <v>3.933581458705695</v>
       </c>
       <c r="S121" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U121" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1170</t>
-        </is>
-      </c>
-      <c r="AA121" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ121" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS121" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1170</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR121" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS121" t="inlineStr"/>
       <c r="AT121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB121" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC121" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -20916,7 +20902,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -20965,98 +20951,23 @@
       <c r="O122" t="n">
         <v>1</v>
       </c>
+      <c r="R122" t="n">
+        <v>0.01778809170864137</v>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U122" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1170</t>
         </is>
       </c>
-      <c r="V122" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1170</t>
-        </is>
-      </c>
-      <c r="W122" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X122" t="inlineStr">
-        <is>
-          <t>RSV</t>
-        </is>
-      </c>
-      <c r="Y122" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD122" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE122" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF122" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG122" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH122" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI122" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ122" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK122" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1170.</t>
-        </is>
-      </c>
-      <c r="AM122" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN122" t="b">
-        <v>1</v>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
@@ -21122,6 +21033,240 @@
         </is>
       </c>
       <c r="BC122" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>respiratory-syncytial-virus-infection-(rsv)</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>呼吸道合胞病毒感染</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N123" t="n">
+        <v>1</v>
+      </c>
+      <c r="O123" t="n">
+        <v>1</v>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1170</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1170</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X123" t="inlineStr">
+        <is>
+          <t>RSV</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD123" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE123" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF123" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG123" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI123" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK123" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1170.</t>
+        </is>
+      </c>
+      <c r="AM123" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN123" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO123" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP123" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ123" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1170</t>
+        </is>
+      </c>
+      <c r="AT123" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU123" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV123" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA123" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB123" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC123" t="inlineStr">
         <is>
           <t>cube_csv</t>
         </is>
@@ -21243,7 +21388,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10">
@@ -21253,7 +21398,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11">
@@ -21305,7 +21450,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>235729</v>
+        <v>237605</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d142/2026-2029.xlsx
+++ b/diseases/d142/2026-2029.xlsx
@@ -16003,13 +16003,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>27446</v>
+        <v>27448</v>
       </c>
       <c r="O89" t="n">
-        <v>27446</v>
+        <v>27448</v>
       </c>
       <c r="R89" t="n">
-        <v>100.8039931985402</v>
+        <v>100.8113388221792</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -18402,13 +18402,13 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>18940</v>
+        <v>18996</v>
       </c>
       <c r="O105" t="n">
-        <v>18940</v>
+        <v>18996</v>
       </c>
       <c r="R105" t="n">
-        <v>69.56305586170483</v>
+        <v>69.76873332359793</v>
       </c>
       <c r="S105" t="inlineStr">
         <is>
@@ -20946,13 +20946,13 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O122" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R122" t="n">
-        <v>0.01778809170864137</v>
+        <v>0.03557618341728275</v>
       </c>
       <c r="S122" t="inlineStr">
         <is>
@@ -21105,10 +21105,10 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O123" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U123" t="inlineStr">
         <is>
@@ -21450,7 +21450,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>237605</v>
+        <v>237664</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d142/2026-2029.xlsx
+++ b/diseases/d142/2026-2029.xlsx
@@ -18402,13 +18402,13 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>18996</v>
+        <v>19086</v>
       </c>
       <c r="O105" t="n">
-        <v>18996</v>
+        <v>19086</v>
       </c>
       <c r="R105" t="n">
-        <v>69.76873332359793</v>
+        <v>70.09928638735471</v>
       </c>
       <c r="S105" t="inlineStr">
         <is>
@@ -21450,7 +21450,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>237664</v>
+        <v>237754</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d142/2026-2029.xlsx
+++ b/diseases/d142/2026-2029.xlsx
@@ -16003,13 +16003,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>27448</v>
+        <v>27449</v>
       </c>
       <c r="O89" t="n">
-        <v>27448</v>
+        <v>27449</v>
       </c>
       <c r="R89" t="n">
-        <v>100.8113388221792</v>
+        <v>100.8150116339987</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -18402,13 +18402,13 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>19086</v>
+        <v>19085</v>
       </c>
       <c r="O105" t="n">
-        <v>19086</v>
+        <v>19085</v>
       </c>
       <c r="R105" t="n">
-        <v>70.09928638735471</v>
+        <v>70.0956135755352</v>
       </c>
       <c r="S105" t="inlineStr">
         <is>

--- a/diseases/d142/2026-2029.xlsx
+++ b/diseases/d142/2026-2029.xlsx
@@ -18402,13 +18402,13 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>19085</v>
+        <v>19096</v>
       </c>
       <c r="O105" t="n">
-        <v>19085</v>
+        <v>19096</v>
       </c>
       <c r="R105" t="n">
-        <v>70.0956135755352</v>
+        <v>70.13601450554991</v>
       </c>
       <c r="S105" t="inlineStr">
         <is>
@@ -21450,7 +21450,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>237754</v>
+        <v>237765</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d142/2026-2029.xlsx
+++ b/diseases/d142/2026-2029.xlsx
@@ -21272,6 +21272,151 @@
         </is>
       </c>
     </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>respiratory-syncytial-virus-infection-(rsv)</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>呼吸道合胞病毒感染</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N124" t="n">
+        <v>2289</v>
+      </c>
+      <c r="O124" t="n">
+        <v>2289</v>
+      </c>
+      <c r="R124" t="n">
+        <v>1.869674444918039</v>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP124" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR124" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr"/>
+      <c r="AT124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU124" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV124" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA124" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB124" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC124" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21305,7 +21450,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -21388,7 +21533,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10">
@@ -21398,7 +21543,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11">
@@ -21450,7 +21595,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>237765</v>
+        <v>240054</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d142/2026-2029.xlsx
+++ b/diseases/d142/2026-2029.xlsx
@@ -20946,13 +20946,13 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O122" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R122" t="n">
-        <v>0.03557618341728275</v>
+        <v>0.05336427512592412</v>
       </c>
       <c r="S122" t="inlineStr">
         <is>
@@ -21105,10 +21105,10 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O123" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U123" t="inlineStr">
         <is>
@@ -21595,7 +21595,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>240054</v>
+        <v>240055</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d142/2026-2029.xlsx
+++ b/diseases/d142/2026-2029.xlsx
@@ -18402,13 +18402,13 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>19096</v>
+        <v>19107</v>
       </c>
       <c r="O105" t="n">
-        <v>19096</v>
+        <v>19107</v>
       </c>
       <c r="R105" t="n">
-        <v>70.13601450554991</v>
+        <v>70.17641543556464</v>
       </c>
       <c r="S105" t="inlineStr">
         <is>
@@ -21595,7 +21595,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>240055</v>
+        <v>240066</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d142/2026-2029.xlsx
+++ b/diseases/d142/2026-2029.xlsx
@@ -16003,13 +16003,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>27449</v>
+        <v>27450</v>
       </c>
       <c r="O89" t="n">
-        <v>27449</v>
+        <v>27450</v>
       </c>
       <c r="R89" t="n">
-        <v>100.8150116339987</v>
+        <v>100.8186844458182</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -18402,13 +18402,13 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>19107</v>
+        <v>19109</v>
       </c>
       <c r="O105" t="n">
-        <v>19107</v>
+        <v>19109</v>
       </c>
       <c r="R105" t="n">
-        <v>70.17641543556464</v>
+        <v>70.18376105920366</v>
       </c>
       <c r="S105" t="inlineStr">
         <is>
@@ -20946,13 +20946,13 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O122" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R122" t="n">
-        <v>0.05336427512592412</v>
+        <v>0.07115236683456549</v>
       </c>
       <c r="S122" t="inlineStr">
         <is>
@@ -21105,10 +21105,10 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O123" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U123" t="inlineStr">
         <is>
@@ -21412,6 +21412,151 @@
         </is>
       </c>
       <c r="BC124" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>respiratory-syncytial-virus-infection-(rsv)</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>呼吸道合胞病毒感染</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N125" t="n">
+        <v>2522</v>
+      </c>
+      <c r="O125" t="n">
+        <v>2522</v>
+      </c>
+      <c r="R125" t="n">
+        <v>2.059990803880862</v>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO125" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP125" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR125" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr"/>
+      <c r="AT125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU125" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV125" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA125" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB125" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC125" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -21450,7 +21595,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -21533,7 +21678,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10">
@@ -21543,7 +21688,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11">
@@ -21595,7 +21740,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>240066</v>
+        <v>242592</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d142/2026-2029.xlsx
+++ b/diseases/d142/2026-2029.xlsx
@@ -16003,13 +16003,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>27450</v>
+        <v>27451</v>
       </c>
       <c r="O89" t="n">
-        <v>27450</v>
+        <v>27451</v>
       </c>
       <c r="R89" t="n">
-        <v>100.8186844458182</v>
+        <v>100.8223572576377</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -20801,13 +20801,13 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>1071</v>
+        <v>11237</v>
       </c>
       <c r="O121" t="n">
-        <v>1071</v>
+        <v>11237</v>
       </c>
       <c r="R121" t="n">
-        <v>3.933581458705695</v>
+        <v>41.27138641594388</v>
       </c>
       <c r="S121" t="inlineStr">
         <is>
@@ -20946,13 +20946,13 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O122" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R122" t="n">
-        <v>0.07115236683456549</v>
+        <v>0.08894045854320688</v>
       </c>
       <c r="S122" t="inlineStr">
         <is>
@@ -21105,10 +21105,10 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O123" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U123" t="inlineStr">
         <is>
@@ -21559,6 +21559,544 @@
       <c r="BC125" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>respiratory-syncytial-virus-infection-(rsv)</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>呼吸道合胞病毒感染</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N126" t="n">
+        <v>2787</v>
+      </c>
+      <c r="O126" t="n">
+        <v>2787</v>
+      </c>
+      <c r="R126" t="n">
+        <v>2.276445031885791</v>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO126" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP126" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR126" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS126" t="inlineStr"/>
+      <c r="AT126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU126" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV126" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA126" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB126" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC126" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>respiratory-syncytial-virus-infection-(rsv)</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>呼吸道合胞病毒感染</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N127" t="n">
+        <v>0</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0</v>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1170</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO127" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP127" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ127" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1170</t>
+        </is>
+      </c>
+      <c r="AT127" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU127" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV127" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA127" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB127" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC127" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>respiratory-syncytial-virus-infection-(rsv)</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>呼吸道合胞病毒感染</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N128" t="n">
+        <v>0</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0</v>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1170</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1170</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X128" t="inlineStr">
+        <is>
+          <t>RSV</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD128" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE128" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF128" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG128" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH128" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI128" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ128" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK128" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1170.</t>
+        </is>
+      </c>
+      <c r="AM128" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN128" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO128" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP128" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ128" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS128" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1170</t>
+        </is>
+      </c>
+      <c r="AT128" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU128" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV128" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA128" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB128" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC128" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -21595,7 +22133,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -21678,7 +22216,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10">
@@ -21688,7 +22226,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11">
@@ -21708,7 +22246,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13">
@@ -21740,7 +22278,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>242592</v>
+        <v>255547</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d142/2026-2029.xlsx
+++ b/diseases/d142/2026-2029.xlsx
@@ -20801,13 +20801,13 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>11237</v>
+        <v>11274</v>
       </c>
       <c r="O121" t="n">
-        <v>11237</v>
+        <v>11274</v>
       </c>
       <c r="R121" t="n">
-        <v>41.27138641594388</v>
+        <v>41.40728045326611</v>
       </c>
       <c r="S121" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>255547</v>
+        <v>255584</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d142/2026-2029.xlsx
+++ b/diseases/d142/2026-2029.xlsx
@@ -29353,13 +29353,13 @@
         </is>
       </c>
       <c r="N169" t="n">
-        <v>19121</v>
+        <v>19122</v>
       </c>
       <c r="O169" t="n">
-        <v>19121</v>
+        <v>19122</v>
       </c>
       <c r="R169" t="n">
-        <v>70.2278348010379</v>
+        <v>70.23150761285743</v>
       </c>
       <c r="S169" t="inlineStr">
         <is>
@@ -38239,7 +38239,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>320737</v>
+        <v>320738</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d142/2026-2029.xlsx
+++ b/diseases/d142/2026-2029.xlsx
@@ -29353,13 +29353,13 @@
         </is>
       </c>
       <c r="N169" t="n">
-        <v>19122</v>
+        <v>19124</v>
       </c>
       <c r="O169" t="n">
-        <v>19122</v>
+        <v>19124</v>
       </c>
       <c r="R169" t="n">
-        <v>70.23150761285743</v>
+        <v>70.23885323649647</v>
       </c>
       <c r="S169" t="inlineStr">
         <is>
@@ -33816,13 +33816,13 @@
         </is>
       </c>
       <c r="N195" t="n">
-        <v>11274</v>
+        <v>11276</v>
       </c>
       <c r="O195" t="n">
-        <v>11274</v>
+        <v>11276</v>
       </c>
       <c r="R195" t="n">
-        <v>41.40728045326611</v>
+        <v>41.41462607690515</v>
       </c>
       <c r="S195" t="inlineStr">
         <is>
@@ -38058,6 +38058,151 @@
       <c r="BC219" t="inlineStr">
         <is>
           <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>respiratory-syncytial-virus-infection-(rsv)</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>D142</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>Respiratory syncytial virus infection (RSV)</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>呼吸道合胞病毒感染</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N220" t="n">
+        <v>2327</v>
+      </c>
+      <c r="O220" t="n">
+        <v>2327</v>
+      </c>
+      <c r="R220" t="n">
+        <v>1.900713164405538</v>
+      </c>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO220" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP220" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR220" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS220" t="inlineStr"/>
+      <c r="AT220" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU220" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV220" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW220" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX220" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY220" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA220" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB220" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC220" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -38094,7 +38239,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -38177,7 +38322,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="10">
@@ -38187,7 +38332,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="11">
@@ -38239,7 +38384,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>320738</v>
+        <v>323069</v>
       </c>
     </row>
     <row r="16">
